--- a/OperadoraNominas/bin/Debug/Archivos/TMM.xlsx
+++ b/OperadoraNominas/bin/Debug/Archivos/TMM.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programacion\Desarrollo\TMMSQ\OperadoraNominas\OperadoraNominas\bin\Debug\Archivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735D6ED2-76B6-4E6E-B8EF-2E173770F966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7594E19A-BBFB-40C3-A4B0-189D5798B698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOMINA" sheetId="38" r:id="rId1"/>
     <sheet name="DETALLE" sheetId="28" r:id="rId2"/>
-    <sheet name="FACT" sheetId="30" r:id="rId3"/>
+    <sheet name="FACT" sheetId="30" state="hidden" r:id="rId3"/>
     <sheet name="Hoja2" sheetId="40" r:id="rId4"/>
     <sheet name="PENSION ALIMENTICIA" sheetId="32" r:id="rId5"/>
     <sheet name="CARATULA" sheetId="42" r:id="rId6"/>
@@ -54,9 +54,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1460,7 +1461,7 @@
     <t>EXCEDENTE</t>
   </si>
   <si>
-    <t>ASESORÍA Y CONSULTORÍA MACHT</t>
+    <t>ADMINISTRACION AYIPEY TECNOLOGY</t>
   </si>
 </sst>
 </file>
@@ -5215,7 +5216,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="FOR"/>
@@ -5248,7 +5249,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="FOR"/>
@@ -5289,7 +5290,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IETU"/>
@@ -5640,9 +5641,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5680,9 +5681,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5715,9 +5716,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5750,9 +5768,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7458,7 +7493,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="28"/>
-    <col min="2" max="2" width="34" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="28" customWidth="1"/>
     <col min="4" max="5" width="11.42578125" style="28"/>
     <col min="6" max="6" width="28.5703125" style="28" bestFit="1" customWidth="1"/>
